--- a/input/Raw_Email.xlsx
+++ b/input/Raw_Email.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Send_Mail_Automation\email_validator_clean\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manas\Downloads\Email_Validator-\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79D7D33-A3BB-4B12-81FF-70D54B606DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF57ED2-C97D-4726-908C-97AECDD94213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Email Results" sheetId="1" r:id="rId1"/>
@@ -19,16 +19,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Email Results'!$B$1:$C$27</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
   <si>
     <t>Brand_Name</t>
   </si>
@@ -175,6 +170,15 @@
   </si>
   <si>
     <t>cs@dentalkart.com</t>
+  </si>
+  <si>
+    <t>manasdikshit48@gmail.com</t>
+  </si>
+  <si>
+    <t>MRD</t>
+  </si>
+  <si>
+    <t>https://manas-ranjan-dikshit.netlify.app/</t>
   </si>
 </sst>
 </file>
@@ -262,7 +266,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
@@ -875,9 +879,15 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
+      <c r="A28" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
@@ -889,6 +899,9 @@
     </row>
   </sheetData>
   <autoFilter ref="B1:C27" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="A28" r:id="rId1" xr:uid="{DBE21CB6-1F71-483D-9D33-350DD324C5EC}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>